--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104474_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104474_W2.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3511</v>
+        <v>4.2443</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6328</v>
+        <v>4.5295</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2817</v>
+        <v>-0.2852</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2074</v>
+        <v>-1.218</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0981</v>
+        <v>-1.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1094</v>
+        <v>-0.1181</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8469</v>
+        <v>0.8131</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6722</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5192</v>
+        <v>1.496</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0543</v>
+        <v>-2.031</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6285</v>
+        <v>-1.6141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4927</v>
+        <v>0.4215</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4506</v>
+        <v>0.4967</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0421</v>
+        <v>-0.0752</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="W2" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5159</v>
+        <v>0.9132</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9643</v>
+        <v>2.3681</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4484</v>
+        <v>-1.4549</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0061</v>
+        <v>0.0128</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4443</v>
+        <v>0.4533</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0641</v>
+        <v>2.0583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4927</v>
+        <v>1.4895</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0702</v>
+        <v>-2.0455</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5901</v>
+        <v>-0.0313</v>
       </c>
       <c r="T3" t="n">
-        <v>1.488</v>
+        <v>0.9032</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.898</v>
+        <v>-0.9345</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1749</v>
+        <v>-0.8383</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8614</v>
+        <v>1.8289</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6865</v>
+        <v>-2.6671</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2751</v>
+        <v>-1.2886</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1556</v>
+        <v>-0.1715</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2643</v>
+        <v>2.2335</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0653</v>
+        <v>0.0442</v>
       </c>
       <c r="L4" t="n">
-        <v>2.199</v>
+        <v>2.1893</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5393</v>
+        <v>-3.5221</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.3185</v>
+        <v>-3.3064</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3308</v>
+        <v>0.3412</v>
       </c>
       <c r="T4" t="n">
-        <v>1.612</v>
+        <v>0.6244</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2813</v>
+        <v>-0.2832</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1487</v>
+        <v>-2.0841</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1374</v>
+        <v>2.8086</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.2862</v>
+        <v>-4.8927</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.718</v>
+        <v>1.2483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2944</v>
+        <v>-1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0124</v>
+        <v>2.5783</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0799</v>
+        <v>4.2542</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8934</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1866</v>
+        <v>4.9372</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.798</v>
+        <v>-3.0059</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.599</v>
+        <v>-0.6471</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.199</v>
+        <v>-2.3588</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5958</v>
+        <v>-1.2218</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1916</v>
+        <v>0.4665</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5958</v>
+        <v>-1.6882</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2534</v>
+        <v>-2.5659</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2284</v>
+        <v>-2.5244</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2907</v>
+        <v>-1.6619</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9376</v>
+        <v>-0.8625</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3798</v>
+        <v>-0.3772</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1649</v>
+        <v>-0.1563</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1476</v>
+        <v>-0.144</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5081</v>
+        <v>0.1555</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3605</v>
+        <v>-0.2995</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5425</v>
+        <v>-1.5479</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4653</v>
+        <v>-2.5347</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0705</v>
+        <v>0.7244</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3947</v>
+        <v>-3.2591</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6218</v>
+        <v>-1.7101</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1314</v>
+        <v>0.293</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4904</v>
+        <v>-2.0031</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4294</v>
+        <v>1.0685</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4688</v>
+        <v>0.8823</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0395</v>
+        <v>0.1862</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1924</v>
+        <v>-2.7786</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6626</v>
+        <v>-0.5893</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5299</v>
+        <v>-2.1893</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.522</v>
+        <v>0.195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.493</v>
+        <v>0.794</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.015</v>
+        <v>-0.5991</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2249</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2249</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8577</v>
+        <v>-2.5741</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7007</v>
+        <v>-1.09</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.157</v>
+        <v>-1.4841</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.4207</v>
+        <v>-2.6083</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9551</v>
+        <v>-2.1229</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4656</v>
+        <v>-0.4854</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.985</v>
+        <v>-0.4486</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7184</v>
+        <v>-1.4759</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2666</v>
+        <v>1.0273</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4357</v>
+        <v>-2.1598</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2368</v>
+        <v>-0.6471</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.199</v>
+        <v>-1.5127</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3362</v>
+        <v>-0.6502</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4185</v>
+        <v>0.4967</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0823</v>
+        <v>-1.1469</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0444</v>
+        <v>-3.1493</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9476</v>
+        <v>-2.0749</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.992</v>
+        <v>-1.0744</v>
       </c>
       <c r="G9" t="n">
-        <v>1.248</v>
+        <v>-4.4266</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3348</v>
+        <v>-1.9613</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5829</v>
+        <v>-2.4653</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2855</v>
+        <v>-2.0072</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6722</v>
+        <v>-1.7312</v>
       </c>
       <c r="L9" t="n">
-        <v>4.9577</v>
+        <v>-0.276</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0374</v>
+        <v>-2.4194</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6626</v>
+        <v>-0.2301</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3749</v>
+        <v>-2.1893</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1752</v>
+        <v>1.0497</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4325</v>
+        <v>1.0704</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7427</v>
+        <v>-0.0207</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.571</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5917</v>
+        <v>-4.0671</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1373</v>
+        <v>-1.3255</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4544</v>
+        <v>-2.7415</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9659</v>
+        <v>-3.9693</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4039</v>
+        <v>-2.4067</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.562</v>
+        <v>-1.5626</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1252</v>
+        <v>-1.1486</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9781</v>
+        <v>-1.9897</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8407</v>
+        <v>-2.8207</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4149</v>
+        <v>-2.4037</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0132</v>
+        <v>0.5364</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1221</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1089</v>
+        <v>-0.4248</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3701</v>
+        <v>-4.5173</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1594</v>
+        <v>-1.3788</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2107</v>
+        <v>-3.1385</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7754</v>
+        <v>-3.7797</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8425</v>
+        <v>-2.8488</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9329</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2816</v>
+        <v>-2.3213</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.975</v>
+        <v>-2.0004</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3067</v>
+        <v>-0.3209</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4938</v>
+        <v>-1.4583</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.57</v>
+        <v>-0.7164</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003</v>
+        <v>0.8335</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.573</v>
+        <v>-1.5499</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5549</v>
+        <v>-5.7419</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1828</v>
+        <v>-1.685</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3721</v>
+        <v>-4.0569</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8269</v>
+        <v>-0.819</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2988</v>
+        <v>-1.2928</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7118</v>
+        <v>1.6855</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L12" t="n">
-        <v>2.159</v>
+        <v>2.1444</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5388</v>
+        <v>-2.5045</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6871</v>
+        <v>-1.6706</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7792</v>
+        <v>-1.9637</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4506</v>
+        <v>0.0926</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3285</v>
+        <v>-2.0564</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.2193</v>
+        <v>-22.8737</v>
       </c>
       <c r="E13" t="n">
-        <v>3.002100000000001</v>
+        <v>3.0434</v>
       </c>
       <c r="F13" t="n">
-        <v>-26.2213</v>
+        <v>-25.9169</v>
       </c>
       <c r="G13" t="n">
-        <v>-18.9491</v>
+        <v>-18.9357</v>
       </c>
       <c r="H13" t="n">
-        <v>-13.0586</v>
+        <v>-13.0676</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.8906</v>
+        <v>-5.8681</v>
       </c>
       <c r="J13" t="n">
-        <v>6.216399999999999</v>
+        <v>5.9666</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.616499999999999</v>
+        <v>-7.7476</v>
       </c>
       <c r="L13" t="n">
-        <v>13.8333</v>
+        <v>13.7141</v>
       </c>
       <c r="M13" t="n">
-        <v>-25.1655</v>
+        <v>-24.9021</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.442</v>
+        <v>-5.32</v>
       </c>
       <c r="O13" t="n">
-        <v>-19.7239</v>
+        <v>-19.5821</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0128</v>
+        <v>-17.0727</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.525399999999999</v>
+        <v>-2.1836</v>
       </c>
       <c r="T13" t="n">
-        <v>6.502600000000001</v>
+        <v>6.8947</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.0281</v>
+        <v>-9.0784</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6105999999999997</v>
+        <v>-0.6161999999999996</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2955</v>
+        <v>7.2542</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.906</v>
+        <v>-7.870400000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0135</v>
+        <v>9.732699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.5519</v>
+        <v>8.5754</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4616</v>
+        <v>1.1574</v>
       </c>
       <c r="G14" t="n">
-        <v>8.168100000000001</v>
+        <v>8.1731</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1542</v>
+        <v>3.159</v>
       </c>
       <c r="I14" t="n">
-        <v>5.0139</v>
+        <v>5.0141</v>
       </c>
       <c r="J14" t="n">
-        <v>8.366899999999999</v>
+        <v>8.337899999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7246</v>
+        <v>1.7097</v>
       </c>
       <c r="L14" t="n">
-        <v>6.6424</v>
+        <v>6.6282</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1989</v>
+        <v>-0.1648</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4297</v>
+        <v>1.4493</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6285</v>
+        <v>-1.6141</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2311</v>
+        <v>-0.0534</v>
       </c>
       <c r="T14" t="n">
-        <v>1.612</v>
+        <v>0.6731</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.381</v>
+        <v>-0.7265</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8576</v>
+        <v>8.751099999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>8.232200000000001</v>
+        <v>8.433400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3746</v>
+        <v>0.3177</v>
       </c>
       <c r="G15" t="n">
-        <v>4.019</v>
+        <v>4.0069</v>
       </c>
       <c r="H15" t="n">
-        <v>1.948</v>
+        <v>1.9473</v>
       </c>
       <c r="I15" t="n">
-        <v>2.071</v>
+        <v>2.0596</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3089</v>
+        <v>4.2747</v>
       </c>
       <c r="K15" t="n">
-        <v>1.257</v>
+        <v>1.2443</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0519</v>
+        <v>3.0304</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2898</v>
+        <v>-0.2678</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7044</v>
+        <v>1.606</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1916</v>
+        <v>1.435</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4872</v>
+        <v>0.171</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6993</v>
+        <v>5.6139</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5054</v>
+        <v>5.9502</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8061</v>
+        <v>-0.3364</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1857</v>
+        <v>3.1766</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1298</v>
+        <v>3.1278</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0559</v>
+        <v>0.0488</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1364</v>
+        <v>5.105</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2339</v>
+        <v>2.2236</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9026</v>
+        <v>2.8815</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9507</v>
+        <v>-1.9284</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8959</v>
+        <v>0.9043</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.8467</v>
+        <v>-2.8326</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4579</v>
+        <v>0.4553</v>
       </c>
       <c r="T16" t="n">
-        <v>0.369</v>
+        <v>0.8452</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8269</v>
+        <v>-0.3899</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2891</v>
+        <v>3.8792</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6548</v>
+        <v>0.8096</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6343</v>
+        <v>3.0696</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7438</v>
+        <v>3.2902</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3883</v>
+        <v>-0.526</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6445</v>
+        <v>3.8161</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7909</v>
+        <v>1.4207</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4923</v>
+        <v>-1.9897</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2985</v>
+        <v>3.4105</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0471</v>
+        <v>1.8694</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8959</v>
+        <v>1.4638</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9431</v>
+        <v>0.4057</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4773</v>
+        <v>-0.2728</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6767</v>
+        <v>0.5757</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1993</v>
+        <v>-0.8485</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8947</v>
+        <v>3.5575</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6097</v>
+        <v>2.4516</v>
       </c>
       <c r="F18" t="n">
-        <v>2.285</v>
+        <v>1.1059</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2898</v>
+        <v>0.7438</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5326</v>
+        <v>2.3759</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8223</v>
+        <v>-1.6321</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4496</v>
+        <v>1.7695</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9781</v>
+        <v>1.4716</v>
       </c>
       <c r="L18" t="n">
-        <v>3.4277</v>
+        <v>0.2979</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8401</v>
+        <v>-1.0257</v>
       </c>
       <c r="N18" t="n">
-        <v>1.4455</v>
+        <v>0.9043</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3946</v>
+        <v>-1.93</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2609</v>
+        <v>1.7454</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3357</v>
+        <v>1.5047</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.5966</v>
+        <v>0.2407</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.879</v>
+        <v>2.7113</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1751</v>
+        <v>2.6937</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2961</v>
+        <v>0.0177</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3416</v>
+        <v>0.3505</v>
       </c>
       <c r="H19" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5384</v>
+        <v>-0.5393</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6156</v>
+        <v>0.6039</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1732</v>
+        <v>0.1724</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4424</v>
+        <v>0.4315</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.274</v>
+        <v>-0.2533</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8815</v>
+        <v>1.6991</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2381</v>
+        <v>1.7743</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3566</v>
+        <v>-0.0752</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7352</v>
+        <v>2.6982</v>
       </c>
       <c r="E20" t="n">
-        <v>1.558</v>
+        <v>2.2419</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1772</v>
+        <v>0.4563</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7541</v>
+        <v>2.7684</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6485</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1165</v>
+        <v>2.1199</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7207</v>
+        <v>3.7112</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>3.0973</v>
+        <v>3.0907</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9666</v>
+        <v>-0.9428</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1608</v>
+        <v>-0.202</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3992</v>
+        <v>0.311</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.513</v>
       </c>
       <c r="V20" t="n">
-        <v>2.4102</v>
+        <v>2.4082</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3943</v>
+        <v>0.5513</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0499</v>
+        <v>-1.73</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4442</v>
+        <v>2.2812</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1877</v>
+        <v>-1.2036</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0115</v>
+        <v>1.0137</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1992</v>
+        <v>-2.2174</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5297</v>
+        <v>-1.5647</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1806</v>
+        <v>-2.2057</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3419</v>
+        <v>0.3611</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9016</v>
+        <v>1.072</v>
       </c>
       <c r="T21" t="n">
-        <v>0.614</v>
+        <v>0.9729</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2876</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8253</v>
+        <v>-1.6007</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7962</v>
+        <v>-0.8001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0291</v>
+        <v>-0.8006</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5475</v>
+        <v>-0.5461</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.974</v>
+        <v>-0.9737</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4265</v>
+        <v>0.4276</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6571</v>
+        <v>-0.6607</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4119</v>
+        <v>-0.1928</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2728</v>
+        <v>-0.0534</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0483</v>
+        <v>-1.7617</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2817</v>
+        <v>-2.0651</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2333</v>
+        <v>0.3035</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8829</v>
+        <v>-0.8954</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5326</v>
+        <v>0.526</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4154</v>
+        <v>-1.4214</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0084</v>
+        <v>-1.0245</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5643</v>
+        <v>0.5548</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0974</v>
+        <v>0.202</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1391</v>
+        <v>0.0975</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3479</v>
+        <v>-2.3535</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0325</v>
+        <v>-0.0083</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3804</v>
+        <v>-2.3451</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1004</v>
+        <v>2.1026</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5757</v>
+        <v>0.5772</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5247</v>
+        <v>1.5254</v>
       </c>
       <c r="J24" t="n">
-        <v>3.0379</v>
+        <v>3.0137</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4298</v>
+        <v>-0.4417</v>
       </c>
       <c r="L24" t="n">
-        <v>3.4678</v>
+        <v>3.4554</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9375</v>
+        <v>-0.9111</v>
       </c>
       <c r="N24" t="n">
-        <v>1.0055</v>
+        <v>1.0189</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.18</v>
+        <v>-0.1797</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4386</v>
+        <v>0.4411</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6185</v>
+        <v>-0.6209</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.322</v>
+        <v>-4.6089</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9705</v>
+        <v>-0.6354</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.3515</v>
+        <v>-3.9736</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.0351</v>
+        <v>-3.0315</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3074</v>
+        <v>0.3019</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.3425</v>
+        <v>-3.3334</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1008</v>
+        <v>-0.1142</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.9689</v>
+        <v>-2.9469</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4082</v>
+        <v>0.416</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.3771</v>
+        <v>-3.3629</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1016</v>
+        <v>0.6015</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2299</v>
+        <v>0.5874</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3315</v>
+        <v>0.0141</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>23.2192</v>
+        <v>27.17039999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>26.2213</v>
+        <v>25.9169</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.002199999999999</v>
+        <v>1.2536</v>
       </c>
       <c r="G26" t="n">
-        <v>18.9493</v>
+        <v>18.9355</v>
       </c>
       <c r="H26" t="n">
-        <v>13.0585</v>
+        <v>13.0674</v>
       </c>
       <c r="I26" t="n">
-        <v>5.8908</v>
+        <v>5.8679</v>
       </c>
       <c r="J26" t="n">
-        <v>25.1655</v>
+        <v>24.9021</v>
       </c>
       <c r="K26" t="n">
-        <v>5.4419</v>
+        <v>5.319899999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>19.7239</v>
+        <v>19.5824</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.2164</v>
+        <v>-5.966699999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>7.616499999999999</v>
+        <v>7.7476</v>
       </c>
       <c r="O26" t="n">
-        <v>-13.8331</v>
+        <v>-13.7141</v>
       </c>
       <c r="P26" t="n">
-        <v>1.1341</v>
+        <v>1.1382</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8785</v>
+        <v>-15.9344</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5254</v>
+        <v>6.4806</v>
       </c>
       <c r="T26" t="n">
-        <v>9.0282</v>
+        <v>9.078500000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.502700000000001</v>
+        <v>-2.5979</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6105</v>
+        <v>0.6162999999999994</v>
       </c>
       <c r="W26" t="n">
-        <v>7.906</v>
+        <v>7.8704</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.295399999999999</v>
+        <v>-7.254200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104474_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104474_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.870400000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104474_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.254200000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
